--- a/update.xlsx
+++ b/update.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KimTsang\Downloads\AI Transportation KPI Dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dchholdingsltd-my.sharepoint.com/personal/kimtsang_dchauriga_com/Documents/Documents/AI Transportation KPI Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8120F8CA-46F8-4ACE-966A-BDABE89BFEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{C7812C41-A0D8-4678-A7FF-CC765441959E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB8B75FC-E18B-461A-88B7-9BFC92427D31}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4821FC99-6406-4C6D-A8AD-C58625E675F3}"/>
+    <workbookView xWindow="-15" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{4821FC99-6406-4C6D-A8AD-C58625E675F3}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>月份</t>
   </si>
@@ -283,14 +283,31 @@
     <t>Clinic/Dispensary/Optical Store
 (ORDER)</t>
   </si>
+  <si>
+    <t>Delivery Drop point
+(CV)</t>
+  </si>
+  <si>
+    <t>Delivery Drop point
+(Pharma)</t>
+  </si>
+  <si>
+    <t>Delivery Drop point
+(Baxter)</t>
+  </si>
+  <si>
+    <t>Delivery Drop point
+(JJM)</t>
+  </si>
+  <si>
+    <t>Delivery Drop point
+(Boston)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-  </numFmts>
   <fonts count="16">
     <font>
       <sz val="12"/>
@@ -406,7 +423,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -428,6 +445,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
@@ -462,7 +485,7 @@
     </xf>
     <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -514,8 +537,11 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -852,7 +878,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDBFB83A-3150-496D-BED3-657404FFAB93}">
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:AA23"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -866,9 +892,11 @@
     <col min="14" max="14" width="17.21875" customWidth="1"/>
     <col min="15" max="20" width="15.33203125" customWidth="1"/>
     <col min="21" max="21" width="12.77734375" customWidth="1"/>
+    <col min="22" max="22" width="1.77734375" style="12" customWidth="1"/>
+    <col min="23" max="27" width="17.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="43.2">
+    <row r="1" spans="1:27" ht="43.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -930,8 +958,24 @@
       <c r="U1" s="13" t="s">
         <v>12</v>
       </c>
+      <c r="V1" s="11"/>
+      <c r="W1" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z1" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA1" s="18" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:27">
       <c r="A2" s="9">
         <v>45839</v>
       </c>
@@ -994,8 +1038,24 @@
         <f>SUM(N2:T2)</f>
         <v>47511</v>
       </c>
+      <c r="V2" s="10"/>
+      <c r="W2" s="14">
+        <v>19120</v>
+      </c>
+      <c r="X2" s="14">
+        <v>7303</v>
+      </c>
+      <c r="Y2" s="14">
+        <v>5945</v>
+      </c>
+      <c r="Z2" s="14">
+        <v>3068</v>
+      </c>
+      <c r="AA2" s="14">
+        <v>692</v>
+      </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:27">
       <c r="A3" s="9">
         <v>45870</v>
       </c>
@@ -1055,11 +1115,27 @@
         <v>242</v>
       </c>
       <c r="U3" s="14">
-        <f t="shared" ref="U3:U13" si="0">SUM(N3:T3)</f>
+        <f t="shared" ref="U3:U14" si="0">SUM(N3:T3)</f>
         <v>46456</v>
       </c>
+      <c r="V3" s="10"/>
+      <c r="W3" s="14">
+        <v>18160</v>
+      </c>
+      <c r="X3" s="14">
+        <v>7212</v>
+      </c>
+      <c r="Y3" s="14">
+        <v>5861</v>
+      </c>
+      <c r="Z3" s="14">
+        <v>3084</v>
+      </c>
+      <c r="AA3" s="14">
+        <v>688</v>
+      </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:27">
       <c r="A4" s="9">
         <v>45901</v>
       </c>
@@ -1122,8 +1198,24 @@
         <f t="shared" si="0"/>
         <v>47086</v>
       </c>
+      <c r="V4" s="10"/>
+      <c r="W4" s="14">
+        <v>18207</v>
+      </c>
+      <c r="X4" s="14">
+        <v>7372</v>
+      </c>
+      <c r="Y4" s="14">
+        <v>5752</v>
+      </c>
+      <c r="Z4" s="14">
+        <v>3825</v>
+      </c>
+      <c r="AA4" s="14">
+        <v>703</v>
+      </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:27">
       <c r="A5" s="9">
         <v>45931</v>
       </c>
@@ -1186,8 +1278,24 @@
         <f t="shared" si="0"/>
         <v>48293</v>
       </c>
+      <c r="V5" s="10"/>
+      <c r="W5" s="14">
+        <v>19055</v>
+      </c>
+      <c r="X5" s="14">
+        <v>7291</v>
+      </c>
+      <c r="Y5" s="14">
+        <v>5688</v>
+      </c>
+      <c r="Z5" s="14">
+        <v>3007</v>
+      </c>
+      <c r="AA5" s="14">
+        <v>685</v>
+      </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:27">
       <c r="A6" s="9">
         <v>45962</v>
       </c>
@@ -1250,8 +1358,24 @@
         <f t="shared" si="0"/>
         <v>47359</v>
       </c>
+      <c r="V6" s="10"/>
+      <c r="W6" s="14">
+        <v>18803</v>
+      </c>
+      <c r="X6" s="14">
+        <v>7052</v>
+      </c>
+      <c r="Y6" s="14">
+        <v>4611</v>
+      </c>
+      <c r="Z6" s="14">
+        <v>3179</v>
+      </c>
+      <c r="AA6" s="14">
+        <v>613</v>
+      </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:27">
       <c r="A7" s="9">
         <v>45992</v>
       </c>
@@ -1314,8 +1438,24 @@
         <f t="shared" si="0"/>
         <v>49097</v>
       </c>
+      <c r="V7" s="10"/>
+      <c r="W7" s="14">
+        <v>18364</v>
+      </c>
+      <c r="X7" s="14">
+        <v>7775</v>
+      </c>
+      <c r="Y7" s="14">
+        <v>5953</v>
+      </c>
+      <c r="Z7" s="14">
+        <v>3672</v>
+      </c>
+      <c r="AA7" s="14">
+        <v>705</v>
+      </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:27">
       <c r="A8" s="9">
         <v>46023</v>
       </c>
@@ -1379,8 +1519,24 @@
         <f t="shared" si="0"/>
         <v>59960</v>
       </c>
+      <c r="V8" s="10"/>
+      <c r="W8" s="14">
+        <v>18649</v>
+      </c>
+      <c r="X8" s="14">
+        <v>7413</v>
+      </c>
+      <c r="Y8" s="14">
+        <v>5738</v>
+      </c>
+      <c r="Z8" s="14">
+        <v>3111</v>
+      </c>
+      <c r="AA8" s="14">
+        <v>685</v>
+      </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:27">
       <c r="A9" s="9">
         <v>46054</v>
       </c>
@@ -1444,8 +1600,24 @@
         <f t="shared" si="0"/>
         <v>47236</v>
       </c>
+      <c r="V9" s="10"/>
+      <c r="W9" s="14">
+        <v>14499</v>
+      </c>
+      <c r="X9" s="14">
+        <v>6560</v>
+      </c>
+      <c r="Y9" s="14">
+        <v>4517</v>
+      </c>
+      <c r="Z9" s="14">
+        <v>2830</v>
+      </c>
+      <c r="AA9" s="14">
+        <v>567</v>
+      </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:27">
       <c r="A10" s="9">
         <v>46082</v>
       </c>
@@ -1509,8 +1681,24 @@
         <f t="shared" si="0"/>
         <v>57704</v>
       </c>
+      <c r="V10" s="10"/>
+      <c r="W10" s="14">
+        <v>18585</v>
+      </c>
+      <c r="X10" s="14">
+        <v>7600</v>
+      </c>
+      <c r="Y10" s="14">
+        <v>5814</v>
+      </c>
+      <c r="Z10" s="14">
+        <v>4406</v>
+      </c>
+      <c r="AA10" s="14">
+        <v>726</v>
+      </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:27">
       <c r="A11" s="9">
         <v>46113</v>
       </c>
@@ -1574,8 +1762,24 @@
         <f t="shared" si="0"/>
         <v>53741</v>
       </c>
+      <c r="V11" s="10"/>
+      <c r="W11" s="14">
+        <v>17857</v>
+      </c>
+      <c r="X11" s="14">
+        <v>7062</v>
+      </c>
+      <c r="Y11" s="14">
+        <v>4929</v>
+      </c>
+      <c r="Z11" s="14">
+        <v>2981</v>
+      </c>
+      <c r="AA11" s="14">
+        <v>615</v>
+      </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:27">
       <c r="A12" s="9">
         <v>46143</v>
       </c>
@@ -1639,8 +1843,24 @@
         <f t="shared" si="0"/>
         <v>53663</v>
       </c>
+      <c r="V12" s="10"/>
+      <c r="W12" s="14">
+        <v>17778</v>
+      </c>
+      <c r="X12" s="14">
+        <v>7067</v>
+      </c>
+      <c r="Y12" s="14">
+        <v>4677</v>
+      </c>
+      <c r="Z12" s="14">
+        <v>3234</v>
+      </c>
+      <c r="AA12" s="14">
+        <v>612</v>
+      </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:27">
       <c r="A13" s="9">
         <v>46174</v>
       </c>
@@ -1704,34 +1924,104 @@
         <f t="shared" si="0"/>
         <v>57479</v>
       </c>
-      <c r="W13" s="17"/>
+      <c r="V13" s="10"/>
+      <c r="W13" s="14">
+        <v>18817</v>
+      </c>
+      <c r="X13" s="14">
+        <v>7773</v>
+      </c>
+      <c r="Y13" s="14">
+        <v>5619</v>
+      </c>
+      <c r="Z13" s="14">
+        <v>4057</v>
+      </c>
+      <c r="AA13" s="14">
+        <v>697</v>
+      </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:27">
       <c r="A14" s="9">
         <v>46204</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="7"/>
+      <c r="B14" s="6">
+        <v>10978</v>
+      </c>
+      <c r="C14" s="6">
+        <v>4.2</v>
+      </c>
+      <c r="D14" s="6">
+        <v>0.33</v>
+      </c>
+      <c r="E14" s="6">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F14" s="6">
+        <v>45487</v>
+      </c>
+      <c r="G14" s="6">
+        <v>3438</v>
+      </c>
+      <c r="H14" s="6">
+        <v>43792</v>
+      </c>
+      <c r="I14" s="6">
+        <v>2849</v>
+      </c>
+      <c r="J14" s="6">
+        <v>1695</v>
+      </c>
+      <c r="K14" s="6">
+        <v>589</v>
+      </c>
+      <c r="L14" s="7">
+        <v>0.99068931391755699</v>
+      </c>
       <c r="M14" s="10"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="14"/>
-      <c r="S14" s="14"/>
-      <c r="T14" s="14"/>
-      <c r="U14" s="14"/>
+      <c r="N14" s="14">
+        <v>32618</v>
+      </c>
+      <c r="O14" s="14">
+        <v>532</v>
+      </c>
+      <c r="P14" s="14">
+        <v>15216</v>
+      </c>
+      <c r="Q14" s="14">
+        <v>15873</v>
+      </c>
+      <c r="R14" s="14">
+        <v>888</v>
+      </c>
+      <c r="S14" s="14">
+        <v>397</v>
+      </c>
+      <c r="T14" s="14">
+        <v>237</v>
+      </c>
+      <c r="U14" s="14">
+        <f t="shared" si="0"/>
+        <v>65761</v>
+      </c>
+      <c r="V14" s="10"/>
+      <c r="W14" s="14">
+        <v>19522</v>
+      </c>
+      <c r="X14" s="14">
+        <v>7836</v>
+      </c>
+      <c r="Y14" s="14">
+        <v>5846</v>
+      </c>
+      <c r="Z14" s="14">
+        <v>3209</v>
+      </c>
+      <c r="AA14" s="14">
+        <v>705</v>
+      </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:27">
       <c r="A15" s="9">
         <v>46235</v>
       </c>
@@ -1755,8 +2045,14 @@
       <c r="S15" s="14"/>
       <c r="T15" s="14"/>
       <c r="U15" s="14"/>
+      <c r="V15" s="10"/>
+      <c r="W15" s="17"/>
+      <c r="X15" s="17"/>
+      <c r="Y15" s="17"/>
+      <c r="Z15" s="17"/>
+      <c r="AA15" s="17"/>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:27">
       <c r="A16" s="9">
         <v>46266</v>
       </c>
@@ -1780,8 +2076,14 @@
       <c r="S16" s="14"/>
       <c r="T16" s="14"/>
       <c r="U16" s="14"/>
+      <c r="V16" s="10"/>
+      <c r="W16" s="17"/>
+      <c r="X16" s="17"/>
+      <c r="Y16" s="17"/>
+      <c r="Z16" s="17"/>
+      <c r="AA16" s="17"/>
     </row>
-    <row r="17" spans="1:21">
+    <row r="17" spans="1:27">
       <c r="A17" s="9">
         <v>46296</v>
       </c>
@@ -1805,8 +2107,14 @@
       <c r="S17" s="14"/>
       <c r="T17" s="14"/>
       <c r="U17" s="14"/>
+      <c r="V17" s="10"/>
+      <c r="W17" s="17"/>
+      <c r="X17" s="17"/>
+      <c r="Y17" s="17"/>
+      <c r="Z17" s="17"/>
+      <c r="AA17" s="17"/>
     </row>
-    <row r="18" spans="1:21">
+    <row r="18" spans="1:27">
       <c r="A18" s="9">
         <v>46327</v>
       </c>
@@ -1830,8 +2138,14 @@
       <c r="S18" s="15"/>
       <c r="T18" s="15"/>
       <c r="U18" s="14"/>
+      <c r="V18" s="10"/>
+      <c r="W18" s="17"/>
+      <c r="X18" s="17"/>
+      <c r="Y18" s="17"/>
+      <c r="Z18" s="17"/>
+      <c r="AA18" s="17"/>
     </row>
-    <row r="19" spans="1:21">
+    <row r="19" spans="1:27">
       <c r="A19" s="9">
         <v>46357</v>
       </c>
@@ -1855,12 +2169,24 @@
       <c r="S19" s="15"/>
       <c r="T19" s="15"/>
       <c r="U19" s="14"/>
+      <c r="V19" s="10"/>
+      <c r="W19" s="17"/>
+      <c r="X19" s="17"/>
+      <c r="Y19" s="17"/>
+      <c r="Z19" s="17"/>
+      <c r="AA19" s="17"/>
     </row>
-    <row r="23" spans="1:21">
+    <row r="23" spans="1:27">
       <c r="H23" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{0c354a30-f421-4d42-bd98-0d86e396d207}" enabled="0" method="" siteId="{0c354a30-f421-4d42-bd98-0d86e396d207}" removed="1"/>
+</clbl:labelList>
 </file>